--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-JP-ServiceRequest.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-JP-ServiceRequest.xlsx
@@ -392,7 +392,7 @@
     <t>ServiceRequest.meta.versionId</t>
   </si>
   <si>
-    <t>バージョン固有の識別子 (Baajon koyū no shikibetsu-shi)</t>
+    <t>バージョン固有の識別子</t>
   </si>
   <si>
     <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
@@ -430,7 +430,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースがどこから来たかを特定する」(Risōsu ga doko kara kita ka o tokutei suru)</t>
+    <t>「リソースがどこから来たかを特定する」</t>
   </si>
   <si>
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
